--- a/Data/预住院总结报表.xlsx
+++ b/Data/预住院总结报表.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,10 +390,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>1610</v>
+      <c r="B3">
+        <v>1761</v>
       </c>
     </row>
   </sheetData>
@@ -403,7 +411,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:32">
@@ -503,99 +511,197 @@
     </row>
     <row r="2" spans="1:32">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>31</v>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-      <c r="D2">
-        <v>21</v>
-      </c>
-      <c r="E2">
+      <c r="B3">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>57</v>
+      </c>
+      <c r="F3">
+        <v>38</v>
+      </c>
+      <c r="G3">
+        <v>58</v>
+      </c>
+      <c r="H3">
         <v>50</v>
       </c>
-      <c r="F2">
-        <v>36</v>
-      </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
-      <c r="H2">
+      <c r="I3">
+        <v>53</v>
+      </c>
+      <c r="J3">
+        <v>62</v>
+      </c>
+      <c r="K3">
+        <v>41</v>
+      </c>
+      <c r="L3">
+        <v>84</v>
+      </c>
+      <c r="M3">
+        <v>67</v>
+      </c>
+      <c r="N3">
+        <v>67</v>
+      </c>
+      <c r="O3">
+        <v>62</v>
+      </c>
+      <c r="P3">
+        <v>65</v>
+      </c>
+      <c r="Q3">
+        <v>63</v>
+      </c>
+      <c r="R3">
+        <v>48</v>
+      </c>
+      <c r="S3">
+        <v>73</v>
+      </c>
+      <c r="T3">
+        <v>61</v>
+      </c>
+      <c r="U3">
+        <v>70</v>
+      </c>
+      <c r="V3">
+        <v>61</v>
+      </c>
+      <c r="W3">
+        <v>84</v>
+      </c>
+      <c r="X3">
+        <v>61</v>
+      </c>
+      <c r="Y3">
+        <v>75</v>
+      </c>
+      <c r="Z3">
+        <v>63</v>
+      </c>
+      <c r="AA3">
+        <v>71</v>
+      </c>
+      <c r="AB3">
         <v>45</v>
       </c>
-      <c r="I2">
+      <c r="AC3">
+        <v>56</v>
+      </c>
+      <c r="AD3">
         <v>52</v>
       </c>
-      <c r="J2">
-        <v>48</v>
-      </c>
-      <c r="K2">
-        <v>37</v>
-      </c>
-      <c r="L2">
-        <v>79</v>
-      </c>
-      <c r="M2">
-        <v>64</v>
-      </c>
-      <c r="N2">
-        <v>61</v>
-      </c>
-      <c r="O2">
-        <v>52</v>
-      </c>
-      <c r="P2">
-        <v>65</v>
-      </c>
-      <c r="Q2">
-        <v>49</v>
-      </c>
-      <c r="R2">
+      <c r="AE3">
         <v>42</v>
       </c>
-      <c r="S2">
-        <v>64</v>
-      </c>
-      <c r="T2">
-        <v>58</v>
-      </c>
-      <c r="U2">
-        <v>66</v>
-      </c>
-      <c r="V2">
-        <v>56</v>
-      </c>
-      <c r="W2">
-        <v>83</v>
-      </c>
-      <c r="X2">
-        <v>55</v>
-      </c>
-      <c r="Y2">
-        <v>62</v>
-      </c>
-      <c r="Z2">
-        <v>62</v>
-      </c>
-      <c r="AA2">
-        <v>71</v>
-      </c>
-      <c r="AB2">
-        <v>45</v>
-      </c>
-      <c r="AC2">
-        <v>56</v>
-      </c>
-      <c r="AD2">
-        <v>52</v>
-      </c>
-      <c r="AE2">
-        <v>42</v>
-      </c>
-      <c r="AF2">
+      <c r="AF3">
         <v>32</v>
       </c>
     </row>
@@ -606,7 +712,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -634,28 +740,54 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>356</v>
-      </c>
-      <c r="C2">
-        <v>267</v>
-      </c>
-      <c r="D2">
-        <v>303</v>
-      </c>
-      <c r="E2">
-        <v>235</v>
-      </c>
-      <c r="F2">
-        <v>252</v>
-      </c>
-      <c r="G2">
-        <v>140</v>
-      </c>
-      <c r="H2">
-        <v>57</v>
+      <c r="B3">
+        <v>402</v>
+      </c>
+      <c r="C3">
+        <v>301</v>
+      </c>
+      <c r="D3">
+        <v>325</v>
+      </c>
+      <c r="E3">
+        <v>243</v>
+      </c>
+      <c r="F3">
+        <v>270</v>
+      </c>
+      <c r="G3">
+        <v>160</v>
+      </c>
+      <c r="H3">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +797,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -975,6 +1107,32 @@
       </c>
       <c r="H12">
         <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>46</v>
+      </c>
+      <c r="C13">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>19</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1081,6 +1239,14 @@
       </c>
       <c r="B12">
         <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1090,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1466,7 +1632,39 @@
         <v>48</v>
       </c>
       <c r="B47">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>49</v>
+      </c>
+      <c r="B48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>51</v>
+      </c>
+      <c r="B50">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
         <v>52</v>
+      </c>
+      <c r="B51">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1492,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>356</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1500,7 +1698,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>267</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1508,7 +1706,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>303</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1516,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1524,7 +1722,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1532,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1540,7 +1738,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1566,7 +1764,7 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>1610</v>
+        <v>1762</v>
       </c>
     </row>
   </sheetData>
@@ -1592,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1680,7 +1878,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>32</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1934,7 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>51</v>
@@ -1769,7 +1967,7 @@
         <v>280</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1779,10 +1977,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1">
         <v>1</v>
       </c>
@@ -1816,43 +2014,90 @@
       <c r="L1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>82</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>176</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>141</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>157</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>109</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>180</v>
       </c>
-      <c r="I2">
+      <c r="I3">
         <v>163</v>
       </c>
-      <c r="J2">
+      <c r="J3">
         <v>137</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <v>201</v>
       </c>
-      <c r="L2">
+      <c r="L3">
         <v>258</v>
+      </c>
+      <c r="M3">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1862,10 +2107,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" spans="1:51">
       <c r="B1">
         <v>1</v>
       </c>
@@ -2004,148 +2249,327 @@
       <c r="AU1">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:47">
+      <c r="AV1">
+        <v>49</v>
+      </c>
+      <c r="AW1">
+        <v>50</v>
+      </c>
+      <c r="AX1">
+        <v>51</v>
+      </c>
+      <c r="AY1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>50</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>47</v>
       </c>
-      <c r="I2">
+      <c r="I3">
         <v>56</v>
       </c>
-      <c r="J2">
+      <c r="J3">
         <v>45</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <v>33</v>
       </c>
-      <c r="L2">
+      <c r="L3">
         <v>27</v>
       </c>
-      <c r="M2">
+      <c r="M3">
         <v>13</v>
       </c>
-      <c r="N2">
+      <c r="N3">
         <v>34</v>
       </c>
-      <c r="O2">
+      <c r="O3">
         <v>43</v>
       </c>
-      <c r="P2">
+      <c r="P3">
         <v>45</v>
       </c>
-      <c r="Q2">
+      <c r="Q3">
         <v>8</v>
       </c>
-      <c r="R2">
+      <c r="R3">
         <v>45</v>
       </c>
-      <c r="S2">
+      <c r="S3">
         <v>48</v>
       </c>
-      <c r="T2">
+      <c r="T3">
         <v>32</v>
       </c>
-      <c r="U2">
+      <c r="U3">
         <v>35</v>
       </c>
-      <c r="V2">
+      <c r="V3">
         <v>22</v>
       </c>
-      <c r="W2">
+      <c r="W3">
         <v>28</v>
       </c>
-      <c r="X2">
+      <c r="X3">
         <v>29</v>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <v>25</v>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <v>26</v>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <v>57</v>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <v>41</v>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <v>40</v>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <v>26</v>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <v>38</v>
       </c>
-      <c r="AF2">
+      <c r="AF3">
         <v>28</v>
       </c>
-      <c r="AG2">
+      <c r="AG3">
         <v>50</v>
       </c>
-      <c r="AH2">
+      <c r="AH3">
         <v>38</v>
       </c>
-      <c r="AI2">
+      <c r="AI3">
         <v>27</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ3">
         <v>29</v>
       </c>
-      <c r="AK2">
+      <c r="AK3">
         <v>33</v>
       </c>
-      <c r="AL2">
+      <c r="AL3">
         <v>41</v>
       </c>
-      <c r="AM2">
+      <c r="AM3">
         <v>9</v>
       </c>
-      <c r="AN2">
+      <c r="AN3">
         <v>35</v>
       </c>
-      <c r="AO2">
+      <c r="AO3">
         <v>51</v>
       </c>
-      <c r="AP2">
+      <c r="AP3">
         <v>64</v>
       </c>
-      <c r="AQ2">
+      <c r="AQ3">
         <v>56</v>
       </c>
-      <c r="AR2">
+      <c r="AR3">
         <v>59</v>
       </c>
-      <c r="AS2">
+      <c r="AS3">
         <v>75</v>
       </c>
-      <c r="AT2">
+      <c r="AT3">
         <v>64</v>
       </c>
-      <c r="AU2">
-        <v>52</v>
+      <c r="AU3">
+        <v>53</v>
+      </c>
+      <c r="AV3">
+        <v>46</v>
+      </c>
+      <c r="AW3">
+        <v>42</v>
+      </c>
+      <c r="AX3">
+        <v>42</v>
+      </c>
+      <c r="AY3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
